--- a/doc/result/KL_AI자료_2026-08/AI 영업비밀 관리시스템 구축 사업 - 기능요구사항 - AI 파트 (세부분할)_구현현황_기입.xlsx
+++ b/doc/result/KL_AI자료_2026-08/AI 영업비밀 관리시스템 구축 사업 - 기능요구사항 - AI 파트 (세부분할)_구현현황_기입.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" s="10">
+    <row r="6" ht="60" customHeight="1" s="10">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>FUN-003-②</t>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>수집·변환 도구는 완결. 대량 실데이터 확보는 외부동의 대기(AI Hub #580 신청 동결, KOIPA 최신 가이드 발주처 회신 의존)</t>
+          <t>수집·변환 도구는 완결. 대량 실데이터 확보는 외부동의 대기 — AI Hub #580(행정문서, 예상 5,000건·1.5GB)은 사전 신청·승인 필요(승인 1~2주 소요)로 신청 동결 상태, KOIPA 최신 가이드는 발주처 회신 의존. 기술 이슈가 아닌 신청·승인 절차 건으로 명의·활용범위 확정 시 즉시 수집 가능</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" s="10">
+    <row r="8" ht="210" customHeight="1" s="10">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>FUN-003-④</t>
@@ -736,12 +736,18 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>프롬프트 체인 기능은 generator.py(SYSTEM_PROMPT/USER_TEMPLATE_V2·temperature 단계강화 재시도)로 구현·동작. pyproject에 langchain 의존성 선언</t>
+          <t>프롬프트 체인 기능은 generator.py(SYSTEM_PROMPT/USER_TEMPLATE_V2·temperature 단계강화 재시도)로 구현·동작. pyproject에 langchain 의존성 선언(선택 extra [orchestration], 운영 이미지 미설치)</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>정직성 유의: 요건이 명시한 LangChain 프레임워크는 실제 미사용(src 전체 import 0건, 프레임워크 비종속 자체 어댑터로 대체). LangChain 채택은 본개발 결정사항</t>
+          <t>정직성 유의: 요건이 명시한 LangChain 프레임워크는 실제 미사용(src 전체 import 0건, 프레임워크 비종속 자체 어댑터로 대체). 기능 미구현이 아니라 구현 수단의 차이이며, 미사용 사유는 다음 5가지.
+① 폐쇄망 동결 번들 원칙 — 운영 이미지는 .[psh,otel,jwt,hwp,hwp-tables,xls]만 설치(Dockerfile.api.prod). langchain은 선택 extra [orchestration]에만 선언되어 배포본 미포함. 에어갭 반입 시 langchain-core·langchain-protocol·langgraph·provider 패키지까지 의존성 트리 전체를 사전 반입해야 함.
+② 다중배포 라이선스·SBOM 부담 — 다수 기업 폐쇄망 배포 구조상 의존성 1개 추가는 트리 전체가 라이선스 검토·SBOM 등재 대상.
+③ 필요 표면적이 작음 — 등급 결정 핫패스는 LLM-free, LLM 사용처는 합성문서 생성·라벨링 보조에 한정. 단일 프롬프트+temperature 재시도로 요건 충족되어 체인·에이전트 추상화 실익 없음.
+④ 요구 통제를 자체 어댑터가 직접 보유 — adapters/llm/base.py가 호출 1건당 토큰·비용·지연·실패코드를 UsageRecord로 DB(llm_usage) 적재, full-jitter 지수 백오프를 provider 공통 통제. LangChain 경유 시 콜백 계층 추가.
+⑤ 온프렘·상용 단일 인터페이스 — vLLM·Ollama·LM Studio를 상용 3종과 동일 Protocol로 다루는 build_provider()가 FUN-003-③·⑥ 근거와 동일 코드. 프레임워크 비종속이 'LLM 교체 시 코드 무변경' 요건에 더 직접적.
+향후 채택 시 build_provider() 위 어댑터 방식으로 대응 가능하며 번들 의존성·라이선스 검토서 갱신 수반. 채택은 본개발 결정사항.</t>
         </is>
       </c>
     </row>

--- a/doc/result/KL_AI자료_2026-08/AI 영업비밀 관리시스템 구축 사업 - 기능요구사항 - AI 파트 (세부분할)_구현현황_기입.xlsx
+++ b/doc/result/KL_AI자료_2026-08/AI 영업비밀 관리시스템 구축 사업 - 기능요구사항 - AI 파트 (세부분할)_구현현황_기입.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>m1_synthesis/generator.py(등급별 상황프롬프트·PII가드·JSON 재시도)·p3_generate_synthetic.py(등급×도메인×길이 배치생성+합격판정)·POST /synth/generate·synthesize_batch 워커·test_m1_synthesis.py</t>
+          <t>m1_synthesis/generator.py(등급별 상황프롬프트·PII가드·JSON 재시도)·p3_generate_synthetic.py(등급×도메인×길이 배치생성+합격판정)·POST /synth/generate·synthesize_batch 워커·test_m1_synthesis.py·admin.html §N 합성 샘플 생성 화면(등급·도메인·건수·provider 폼)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -665,29 +665,29 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="10">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>FUN-003-②</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>AI Hub, 공공데이터 포털을 활용하여 실제 데이터와 유사한 모의 학습·테스트 데이터를 구축할 수 있어야 한다.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>collect_public_data.py(공공데이터포털·AI Hub#580·DART·law.go.kr 수집·검증·변환)·kipris_aihub_nkt_ingest.py(특허 프록시)·p2_koipa_corpus_builder.py(KOIPA CSV→평가코퍼스). 특허프록시·KOIPA 일부는 실적재·학습 반영</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>수집·변환 도구는 완결. 대량 실데이터 확보는 외부동의 대기 — AI Hub #580(행정문서, 예상 5,000건·1.5GB)은 사전 신청·승인 필요(승인 1~2주 소요)로 신청 동결 상태, KOIPA 최신 가이드는 발주처 회신 의존. 기술 이슈가 아닌 신청·승인 절차 건으로 명의·활용범위 확정 시 즉시 수집 가능</t>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>collect_public_data.py(수집·검증·JSONL 변환)·kipris_aihub_nkt_ingest.py·p2_oss_corpus_builder.py·p2_koipa_corpus_builder.py. 실적재 — ①AI Hub #71739 「국가중점기술 분류 대응 특허데이터」 공개특허 4,800건(KIPO 국가중점기술 소분류 라벨 → TS/S1 근거) 적재 → 학습셋 7,200행 실반영(v4 step2·step3) ②법원 공개판례 3,332건(CC BY 4.0) + 영업비밀 관련 판결 358건 ③학습 미포함 공개 판례 400건 = v5 배포 게이트 과분류 측정셋</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>공개문서는 학습에 투입하면 과분류를 유발해, 학습셋에서 분리하고 배포 게이트의 과분류 측정셋으로 사용(측정치는 「분류 정확도 테스트방식」 참조). 남은 과제는 데이터 양이 아니라 고등급(TS/S1) 실문서 텍스처로, 공개셋으로는 확보 불가 — 운영단계 현장 수집 과제</t>
         </is>
       </c>
     </row>
@@ -719,27 +719,27 @@
       </c>
     </row>
     <row r="8" ht="210" customHeight="1" s="10">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>FUN-003-④</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>LangChain 기반 프롬프트 체인을 구성하여 보안등급 기준에 맞는 문서를 자동 생성할 수 있어야 한다.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>완료(대체구현)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>프롬프트 체인 기능은 generator.py(SYSTEM_PROMPT/USER_TEMPLATE_V2·temperature 단계강화 재시도)로 구현·동작. pyproject에 langchain 의존성 선언(선택 extra [orchestration], 운영 이미지 미설치)</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>정직성 유의: 요건이 명시한 LangChain 프레임워크는 실제 미사용(src 전체 import 0건, 프레임워크 비종속 자체 어댑터로 대체). 기능 미구현이 아니라 구현 수단의 차이이며, 미사용 사유는 다음 5가지.
 ① 폐쇄망 동결 번들 원칙 — 운영 이미지는 .[psh,otel,jwt,hwp,hwp-tables,xls]만 설치(Dockerfile.api.prod). langchain은 선택 extra [orchestration]에만 선언되어 배포본 미포함. 에어갭 반입 시 langchain-core·langchain-protocol·langgraph·provider 패키지까지 의존성 트리 전체를 사전 반입해야 함.
@@ -774,7 +774,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>라벨=목표등급을 룰라벨러 예측과 대조검증. 저품질 출처(noop/nonjson)는 학습 하드배제(위생게이트, 무음드롭 없이 사유별 카운트)</t>
+          <t>라벨=목표등급을 룰라벨러 예측과 대조검증. 저품질 출처(noop/nonjson)는 학습 하드배제(위생게이트, 무음드롭 없이 사유별 카운트). 검수 화면에서 확정 등급을 목표등급과 다르게 고르면 corrected_grade 로 반영돼 그 등급으로 학습행이 생성됩니다.</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>synthesize_batch(→tb_sample_documents pending_review)·GET /synth/queue·POST /synth/{id}/review(admin/reviewer 인증)·build_training_rows(승인분→학습행)·test_synth_worker_persist.py</t>
+          <t>synthesize_batch(→tb_sample_documents pending_review)·GET /synth/queue·POST /synth/{id}/review(admin/reviewer 인증)·build_training_rows(승인분→학습행)·test_synth_worker_persist.py·admin.html §N 검수 큐 화면(미리보기·확정등급 선택·승인/반려 버튼)·test_admin_console_screens.py</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>generate→queue→review→train 루프 완결·테스트. 승인행의 버전화 데이터셋 최종 바인딩은 빌드타임 단계</t>
+          <t>generate→queue→review→train 루프 완결·테스트. 관리자 콘솔에 생성·검수 화면 제공(2026-08-02 추가 — 그 전에는 API 전용이었음). 승인행의 버전화 데이터셋 최종 바인딩은 빌드타임 단계</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>trainer compute_metrics(sklearn Acc·Precision·Recall·F1 macro·confusion_matrix·등급별 FNR)→report.json+MLflow·m6_evaluation/metrics.py·report.py(HTML+CM PNG)</t>
+          <t>trainer compute_metrics(sklearn Acc·Precision·Recall·F1 macro·confusion_matrix·등급별 FNR)→report.json+MLflow·p1_train_classifier.py --report(Markdown)·m6_evaluation/metrics.py·report.py(HTML+CM PNG)·scripts/render_eval_report.py(HTML/PNG 산출 CLI)</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Acc/P/R/F1/CM/FNR 리포트 완비(JSON/Markdown/HTML+PNG). FNR(고등급 미탐)이 핵심 KPI로 별도 강조 산출</t>
+          <t>Acc/P/R/F1/CM/FNR 리포트 완비 — JSON(report.json)·Markdown(p1_classifier_report.md)은 학습 파이프라인이 자동 산출, HTML+CM PNG는 render_eval_report.py CLI로 산출(2026-08-02 진입점 추가). FNR(고등급 미탐)이 핵심 KPI로 별도 강조 산출</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>api/schema_admin.py GET·PUT /schema/grades·schema_admin_service.put(추가=신규 level·변경=upsert·삭제=is_active=False 소프트삭제·requires_retraining·캐시무효화)·GradeRegistry DB주도·test_kl_integration.py</t>
+          <t>api/schema_admin.py GET·PUT /schema/grades·schema_admin_service.put(추가=신규 level·변경=upsert·삭제=is_active=False 소프트삭제·requires_retraining·캐시무효화)·GradeRegistry DB주도·test_kl_integration.py·admin.html §E 등급체계 관리 화면(행 추가/편집/삭제 + 비활성 경고 + 재학습 필요 배너)·test_admin_console_screens.py</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>API·서비스·DB 완비. 삭제=소프트삭제(감사·기존분류 보존). 추가/변경/삭제는 PUT API(admin.html은 조회만·편집폼 부재). 등급 구조변경 시 requires_retraining=True 통지</t>
+          <t>API·서비스·DB·화면 완비. 삭제=소프트삭제(감사·기존분류 보존). 관리자 콘솔에서 등급 추가/변경/삭제를 직접 편집·저장(PUT)합니다(2026-08-02 편집 화면 추가 — 그 전에는 조회 전용). PUT은 목록 전체 치환이라 표에서 뺀 등급은 비활성 처리되며 저장 전 확인 경고가 뜹니다. 등급 구조변경 시 requires_retraining=True 통지</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>m2_preprocess/extractor.py extract() 확장자 라우터(HWP/HWPX/DOCX/DOC/PDF/XLSX/XLS/PPTX/이미지OCR)·rhwp·python-docx·pdfminer→PyMuPDF→Tesseract 3단·test_parser_support_matrix.py·백서 §04</t>
+          <t>m2_preprocess/extractor.py extract() 확장자 라우터(HWP/HWPX/DOCX/DOC/PDF/XLSX/XLS/PPTX)·PDF=pdfminer.six(배포 기본)·PyMuPDF→Tesseract OCR 폴백은 코드에 구현되어 있으나 옵트인 extra([pdf-agpl]·[ocr])로 배포 이미지 미포함·test_parser_support_matrix.py·백서 §04</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>핵심 포맷 자동추출. 일부 선택의존성 graceful-degrade(.hwp 표셀=pyhwp 옵트인, .xls=xlrd, .doc=antiword CLI). 미설치는 예외 대신 error 필드로 안전 degrade</t>
+          <t>핵심 포맷 자동추출. 일부 선택의존성 graceful-degrade(.hwp 표셀=unhwp(MIT) 옵트인 extra [hwp-tables] — 구 pyhwp(AGPLv3+) 경로는 2026-08-01 제거, .xls=xlrd, .doc=antiword CLI). 미설치는 예외 대신 error 필드로 안전 degrade</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>DOCX 머리글/바닥글/표/글상자·HWPX 표셀·PDF 표(pdfplumber)·PPTX 슬라이드·Excel 병합셀 세로전파·ExtractedTable 구조보존</t>
+          <t>DOCX 머리글/바닥글/표/글상자·HWPX 표셀·PDF 표(pdfplumber — 옵트인 extra [pdf-tables])·PPTX 슬라이드·Excel 병합셀 세로전파·ExtractedTable 구조보존</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>본문+머리/바닥/표/글상자를 폐기 않고 라벨링 포착(표 속 등급·원가 미탐 방지). .hwp 표셀 누락은 table_coverage=incomplete 신호(등급 불변, FNR-safe)</t>
+          <t>본문+머리/바닥/표/글상자를 폐기 않고 라벨링 포착(표 속 등급·원가 미탐 방지). .hwp 표셀 누락은 table_coverage=incomplete 신호(등급 불변, FNR-safe). PDF 표는 pdfplumber 미설치 시 pdf_table_extractor_unavailable 경고 후 degrade(본문 텍스트는 정상 추출)</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>seeds.py FACTOR_SEEDS(S 비공지성/V 경제가치/M 비밀관리, 405 키워드 factor 속성)·EvaluationFactors·ClassificationEvidence.factor_id(근거↔요소 FK)·explain.py 요소분해</t>
+          <t>seeds.py FACTOR_SEEDS(S 비공지성/V 경제가치/M 비밀관리, KEYWORD_SEEDS 404건에 factor 속성)·EvaluationFactors·ClassificationEvidence.factor_id(근거↔요소 FK)·explain 요소분해</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>키워드(seeds 405+tb_level_keywords)·표현패턴(rule_engine exact/regex/semantic)·메타데이터(source-prior cap·metadata-floor security_marking/access_scope ICD §4)·학습+추론 활용</t>
+          <t>키워드(코드 시드 404건 + tb_level_keywords)·표현패턴(rule_engine exact/regex/semantic)·메타데이터(source-prior cap·metadata-floor security_marking/access_scope ICD §4)·학습+추론 활용</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>api/keyword_admin.py /admin/keywords CRUD(soft delete·RBAC)·서빙 룰엔진 라이브 핫리로드·schema_admin requires_retraining·DB주도 seeds(코드 무변경)·test_keyword_admin.py</t>
+          <t>api/keyword_admin.py /admin/keywords CRUD(soft delete·RBAC)·서빙 룰엔진 라이브 핫리로드·schema_admin requires_retraining·DB주도 seeds(코드 무변경)·test_keyword_admin.py·admin.html §T 태깅 규칙 관리 화면(등급·요소 필터·추가·수정·비활성)·test_admin_console_screens.py</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>키워드 변경=라이브 핫리로드 즉시 반영. 등급체계 개정=requires_retraining 신호(모델 재학습은 별도 거버넌스). 정책개정 유연 수정·확장 충족</t>
+          <t>관리자 콘솔에서 키워드·표현패턴을 직접 추가/수정/비활성합니다(2026-08-02 화면 추가 — 그 전에는 API 전용). 변경은 룰엔진 핫리로드로 재기동 없이 반영되며, 응답 serving_reloaded는 요청을 처리한 워커 기준입니다 — 다중 워커(gunicorn) 운영에서는 나머지 워커가 재기동·다음 리로드까지 이전 규칙을 유지합니다(화면에 명시). DB 키워드 0건이면 룰엔진이 코드 시드 404건으로 폴백하며, 첫 키워드 추가 시 코드 시드를 DB로 자동 승격해 시드 붕괴를 차단합니다. 등급체계 개정=requires_retraining 신호(모델 재학습은 별도 거버넌스)</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>m6_evaluation/metrics.py(sklearn Accuracy·Precision·Recall·F1 macro+등급별·FNR·방향성 미탐 FNR)·MetricsResult·GET /metrics/latest·history·admin.html 카드+등급별 FNR·report.py 표</t>
+          <t>m6_evaluation/metrics.py(sklearn Accuracy·Precision·Recall·F1 macro+등급별·FNR·방향성 미탐 FNR)·MetricsResult·GET /metrics/latest·history·admin.html 지표 카드 6종(정확도·정밀도·재현율·F1·FNR·표본)+등급별 FNR+이력 표·report.py 표</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>다양한 지표 산출·API·UI 완비. precision/recall_macro는 API 응답·리포트에 포함. 실정답 부재(sample=0) 시 N/A 정직 처리</t>
+          <t>다양한 지표 산출·API·UI 완비. 정밀도·재현율은 지표 카드와 이력 표에 직접 표시됩니다(2026-08-02 카드 추가 — 그 전에는 API 응답·리포트에만 있었음). 실정답 부재(sample=0) 시 N/A 정직 처리</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>등급별 CM 시각 확인 완비. 라이브 시각화=admin 콘솔 격자 테이블. report.py PNG 렌더러는 standalone 모듈(API 미배선, CLI 호출)</t>
+          <t>등급별 CM 시각 확인 완비. 라이브 시각화=admin 콘솔 격자 테이블. report.py PNG/HTML 렌더러는 API에 배선하지 않고 scripts/render_eval_report.py CLI로 산출합니다(2026-08-02 CLI 추가 — 그 전에는 호출자가 단위 테스트뿐이었음)</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>완료 31 · 진행중 2 (총 33항목). 진행중=FUN-003-②(실데이터 대량수집 외부동의 대기)·FUN-003-④(LangChain 프레임워크 미사용·자체 어댑터 대체). 근거는 실제 소스 대조 확인(2026-07-29).</t>
+          <t>완료 32 · 완료(대체구현) 1 (총 33항목). FUN-003-④는 요건이 요구한 프롬프트 체인 기능이 동작하되 LangChain 프레임워크 대신 자체 어댑터로 구현한 건이라 완료(대체구현)으로 표기. FUN-003-②는 AI Hub #71739 실활용(공개특허 4,800건→학습 7,200행)·공개판례 3,332건 구축·배포 게이트 평가 반영이 확인되어 완료 판정(대량 실데이터 확장은 운영단계 과제로 이월). 근거는 실제 소스 대조 확인(2026-07-29 · 최종 반영 2026-08-02). 2026-08-02 관리자 화면 보완: 등급체계 편집(FUN-005-①)·합성 샘플 검수(FUN-003-⑦)·태깅 규칙 관리(FUN-023-④)·정밀도/재현율 지표 카드(FUN-024-①) 화면 신규 추가, 평가 리포트 HTML/PNG 산출 CLI(FUN-004-⑤·FUN-024-③) 추가. 정정 반영: .hwp 표셀 의존성 pyhwp→unhwp(FUN-022-①), 키워드 시드 405→404건(FUN-023-②③), 룰엔진 핫리로드의 다중 워커 한계 명시(FUN-023-④).</t>
         </is>
       </c>
     </row>
